--- a/PDT_PI_2.xlsx
+++ b/PDT_PI_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ecole\Projet 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D5CAF6-8930-4A92-86A1-2469DB557688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC4C996-46C1-4713-8F95-18E35D132964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CF7E7B00-0B90-4AA1-96DC-F02D56B415EB}"/>
   </bookViews>
@@ -1395,21 +1395,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100579959CCCCA5C544BBD30F9226CE8516" ma:contentTypeVersion="4" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="18a3a6cb6fca627387261b481e951241">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88fb2577-ad7a-4d43-8167-cef18aea1aa3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c32280d31556b1ec6db52af4e194afa7" ns2:_="">
     <xsd:import namespace="88fb2577-ad7a-4d43-8167-cef18aea1aa3"/>
@@ -1553,24 +1538,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56D71B08-E827-483B-9150-DAAFA24A9B1C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF659F0-93B9-47A9-A708-8A09E9128827}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFFA3822-A47A-4455-B0B9-162E8DE8BA4F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1586,4 +1569,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF659F0-93B9-47A9-A708-8A09E9128827}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56D71B08-E827-483B-9150-DAAFA24A9B1C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/PDT_PI_2.xlsx
+++ b/PDT_PI_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/04678f91986f9bfb/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F93117C-D468-43B3-9F8C-08638999D9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BE277D-FAFF-4B6E-AA1F-C5838922CE00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CF7E7B00-0B90-4AA1-96DC-F02D56B415EB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="57">
   <si>
     <t>Plan de tests</t>
   </si>
@@ -195,6 +195,18 @@
   </si>
   <si>
     <t>Vérifier que les mesures affichées sur l'écran concordent avec les mesures reçues dans le fichier JSON.</t>
+  </si>
+  <si>
+    <t>reussir à trasmettre des données grace aux PCB ( transmission UART1-&gt; UART2</t>
+  </si>
+  <si>
+    <t>reussir à envoyer les information du PCB au PI et les affichées sur l'écran</t>
+  </si>
+  <si>
+    <t>L'affichage se lance sur l'écran du pc apres avoir lancer le code dans l'invite des commandes</t>
+  </si>
+  <si>
+    <t>Les information se sont bien affichées au bon endroit ( case vitesse, alim , voyant freinage….)</t>
   </si>
 </sst>
 </file>
@@ -418,7 +430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -473,6 +485,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -759,13 +780,9 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3E4F9C66-3C4F-4FED-86C7-317DD6AF871B}" name="Table3" displayName="Table3" ref="B10:H22" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11">
-  <autoFilter ref="B10:H22" xr:uid="{3E4F9C66-3C4F-4FED-86C7-317DD6AF871B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3E4F9C66-3C4F-4FED-86C7-317DD6AF871B}" name="Table3" displayName="Table3" ref="B10:H24" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11">
+  <autoFilter ref="B10:H24" xr:uid="{3E4F9C66-3C4F-4FED-86C7-317DD6AF871B}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{21BD1CA3-33DE-44AA-9EB4-FC84914AA01E}" name="Fonction" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{40F1DB91-EE19-4388-9FD9-FC665131A01C}" name="Description du test" dataDxfId="9"/>
@@ -1079,7 +1096,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -1318,128 +1335,150 @@
       <c r="C17" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="18"/>
+      <c r="D17" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>55</v>
+      </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18"/>
       <c r="H17" s="18"/>
     </row>
     <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="16"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+    </row>
+    <row r="19" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B19" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>52</v>
-      </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-    </row>
-    <row r="19" spans="1:8" ht="21" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>40</v>
       </c>
       <c r="D19" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E19" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-    </row>
-    <row r="20" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="E19" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+    </row>
+    <row r="20" spans="1:8" ht="21" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="D20" s="16"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+    </row>
+    <row r="21" spans="1:8" ht="21" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
       <c r="B21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="18" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+    </row>
+    <row r="22" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D24" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E24" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="19"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="20"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="19"/>
-      <c r="C29" s="20"/>
+      <c r="B29" s="20"/>
       <c r="D29" s="20"/>
       <c r="E29" s="20"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B30" s="19"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
+      <c r="D30" s="21"/>
       <c r="E30" s="20"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
@@ -1460,7 +1499,7 @@
       <c r="D33" s="20"/>
       <c r="E33" s="20"/>
     </row>
-    <row r="34" spans="2:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="19"/>
       <c r="C34" s="20"/>
       <c r="D34" s="20"/>
@@ -1472,7 +1511,7 @@
       <c r="D35" s="20"/>
       <c r="E35" s="20"/>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="19"/>
       <c r="C36" s="20"/>
       <c r="D36" s="20"/>
@@ -1480,11 +1519,15 @@
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="19"/>
+      <c r="C37" s="20"/>
       <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="19"/>
+      <c r="C38" s="20"/>
       <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="19"/>
@@ -1493,18 +1536,26 @@
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="19"/>
       <c r="D40" s="20"/>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B41" s="19"/>
+      <c r="D41" s="20"/>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B42" s="19"/>
+      <c r="D42" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C2:C4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D11:D22 G11:G22">
+  <conditionalFormatting sqref="D11:D24 G11:G24">
     <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="Échec">
       <formula>NOT(ISERROR(SEARCH("Échec",D11)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F11:H22">
+  <conditionalFormatting sqref="F11:H24">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>$D11=""</formula>
     </cfRule>
@@ -1512,16 +1563,16 @@
       <formula>$D11="Réussi"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G11:G22 D11:D22">
+  <conditionalFormatting sqref="G11:G24 D11:D24">
     <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Réussi">
       <formula>NOT(ISERROR(SEARCH("Réussi",D11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G22 D11:D22" xr:uid="{FE4B82E2-1996-4D3C-82E2-B8CCB3918355}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G24 D11:D24" xr:uid="{FE4B82E2-1996-4D3C-82E2-B8CCB3918355}">
       <formula1>$J$4:$J$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11:B22" xr:uid="{78441C5B-4219-4854-877A-7D3169F5D56F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11:B24" xr:uid="{78441C5B-4219-4854-877A-7D3169F5D56F}">
       <formula1>$J$8:$J$10</formula1>
     </dataValidation>
   </dataValidations>
@@ -1535,12 +1586,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100579959CCCCA5C544BBD30F9226CE8516" ma:contentTypeVersion="4" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="18a3a6cb6fca627387261b481e951241">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88fb2577-ad7a-4d43-8167-cef18aea1aa3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c32280d31556b1ec6db52af4e194afa7" ns2:_="">
     <xsd:import namespace="88fb2577-ad7a-4d43-8167-cef18aea1aa3"/>
@@ -1684,6 +1729,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1694,22 +1745,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56D71B08-E827-483B-9150-DAAFA24A9B1C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="88fb2577-ad7a-4d43-8167-cef18aea1aa3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFFA3822-A47A-4455-B0B9-162E8DE8BA4F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1727,6 +1762,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56D71B08-E827-483B-9150-DAAFA24A9B1C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="88fb2577-ad7a-4d43-8167-cef18aea1aa3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF659F0-93B9-47A9-A708-8A09E9128827}">
   <ds:schemaRefs>
